--- a/ROSA_vitaSPEC/Data/Analyses_chimiques_4var_en_plus_HR.xlsx
+++ b/ROSA_vitaSPEC/Data/Analyses_chimiques_4var_en_plus_HR.xlsx
@@ -24,9 +24,6 @@
     <t>ech</t>
   </si>
   <si>
-    <t>FFA(%)</t>
-  </si>
-  <si>
     <t>trans.alpha.carotene</t>
   </si>
   <si>
@@ -595,6 +592,9 @@
   </si>
   <si>
     <t>C18.2</t>
+  </si>
+  <si>
+    <t>FFA</t>
   </si>
 </sst>
 </file>
@@ -963,78 +963,78 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B2">
         <v>0.71832663331243773</v>
@@ -1112,7 +1112,7 @@
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3">
         <v>0.49409037578744008</v>
@@ -1190,7 +1190,7 @@
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4">
         <v>0.48144405077532748</v>
@@ -1268,7 +1268,7 @@
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B5">
         <v>0.57456098889732443</v>
@@ -1346,7 +1346,7 @@
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6">
         <v>0.62220273595508391</v>
@@ -1424,7 +1424,7 @@
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7">
         <v>0.54864107571826759</v>
@@ -1502,7 +1502,7 @@
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B8">
         <v>0.55222459470120322</v>
@@ -1580,7 +1580,7 @@
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B9">
         <v>0.89326981321869448</v>
@@ -1658,7 +1658,7 @@
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B10">
         <v>0.80917011051638332</v>
@@ -1736,7 +1736,7 @@
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B11">
         <v>0.53985963479140731</v>
@@ -1814,7 +1814,7 @@
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B12">
         <v>0.51963630662300186</v>
@@ -1892,7 +1892,7 @@
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B13">
         <v>0.83105222628187825</v>
@@ -1970,7 +1970,7 @@
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B14">
         <v>0.58918076749123993</v>
@@ -2048,7 +2048,7 @@
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B15">
         <v>0.47970646827755242</v>
@@ -2126,7 +2126,7 @@
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B16">
         <v>0.68174713762058625</v>
@@ -2204,7 +2204,7 @@
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B17">
         <v>0.83960411769670074</v>
@@ -2282,7 +2282,7 @@
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B18">
         <v>0.78734716235963598</v>
@@ -2360,7 +2360,7 @@
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B19">
         <v>0.81933301512808732</v>
@@ -2438,7 +2438,7 @@
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B20">
         <v>0.54728721988496676</v>
@@ -2516,7 +2516,7 @@
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B21">
         <v>0.60653963798307287</v>
@@ -2594,7 +2594,7 @@
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B22">
         <v>0.55804303194319926</v>
@@ -2672,7 +2672,7 @@
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B23">
         <v>0.52037466224479045</v>
@@ -2750,7 +2750,7 @@
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B24">
         <v>1.3387151896456531</v>
@@ -2828,7 +2828,7 @@
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B25">
         <v>0.83201607528791011</v>
@@ -2906,7 +2906,7 @@
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B26">
         <v>0.89571444412227363</v>
@@ -2984,7 +2984,7 @@
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B27">
         <v>1.0644060133562401</v>
@@ -3062,7 +3062,7 @@
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B28">
         <v>0.70002901742065582</v>
@@ -3140,7 +3140,7 @@
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B29">
         <v>0.76210093803004531</v>
@@ -3218,7 +3218,7 @@
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B30">
         <v>0.60222269380737703</v>
@@ -3296,7 +3296,7 @@
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B31">
         <v>0.63850139468168998</v>
@@ -3374,7 +3374,7 @@
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B32">
         <v>1.023019749752796</v>
@@ -3452,7 +3452,7 @@
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B33">
         <v>0.63485002883066266</v>
@@ -3530,7 +3530,7 @@
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B34">
         <v>0.72667808406515788</v>
@@ -3608,7 +3608,7 @@
     </row>
     <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B35">
         <v>0.64924476058171754</v>
@@ -3686,7 +3686,7 @@
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B36">
         <v>1.0599645380770211</v>
@@ -3764,7 +3764,7 @@
     </row>
     <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B37">
         <v>1.0912260315710871</v>
@@ -3842,7 +3842,7 @@
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B38">
         <v>0.99143755298313851</v>
@@ -3920,7 +3920,7 @@
     </row>
     <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B39">
         <v>0.46293205614239169</v>
@@ -3995,7 +3995,7 @@
     </row>
     <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B40">
         <v>0.77233272431890021</v>
@@ -4073,7 +4073,7 @@
     </row>
     <row r="41" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B41">
         <v>0.96018907765755857</v>
@@ -4151,7 +4151,7 @@
     </row>
     <row r="42" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B42">
         <v>0.94356940832183867</v>
@@ -4229,7 +4229,7 @@
     </row>
     <row r="43" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B43">
         <v>0.9325289694711052</v>
@@ -4307,7 +4307,7 @@
     </row>
     <row r="44" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B44">
         <v>1.1778690390806461</v>
@@ -4385,7 +4385,7 @@
     </row>
     <row r="45" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B45">
         <v>1.0951871004834739</v>
@@ -4463,7 +4463,7 @@
     </row>
     <row r="46" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B46">
         <v>0.68183002415352933</v>
@@ -4541,7 +4541,7 @@
     </row>
     <row r="47" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B47">
         <v>1.1263702405996809</v>
@@ -4619,7 +4619,7 @@
     </row>
     <row r="48" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B48">
         <v>0.6216545728362326</v>
@@ -4697,7 +4697,7 @@
     </row>
     <row r="49" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B49">
         <v>0.62261886433360669</v>
@@ -4775,7 +4775,7 @@
     </row>
     <row r="50" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B50">
         <v>0.64850979340475989</v>
@@ -4850,7 +4850,7 @@
     </row>
     <row r="51" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B51">
         <v>0.81253992623014915</v>
@@ -4928,7 +4928,7 @@
     </row>
     <row r="52" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B52">
         <v>0.54077160912463751</v>
@@ -5006,7 +5006,7 @@
     </row>
     <row r="53" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B53">
         <v>0.65377949247227574</v>
@@ -5084,7 +5084,7 @@
     </row>
     <row r="54" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B54">
         <v>0.54249544195197363</v>
@@ -5162,7 +5162,7 @@
     </row>
     <row r="55" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B55">
         <v>0.57085139787717021</v>
@@ -5240,7 +5240,7 @@
     </row>
     <row r="56" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B56">
         <v>0.67861770625589501</v>
@@ -5318,7 +5318,7 @@
     </row>
     <row r="57" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B57">
         <v>0.81637680058807449</v>
@@ -5396,7 +5396,7 @@
     </row>
     <row r="58" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B58">
         <v>0.53316705079471793</v>
@@ -5474,7 +5474,7 @@
     </row>
     <row r="59" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B59">
         <v>0.82272508008790723</v>
@@ -5552,7 +5552,7 @@
     </row>
     <row r="60" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B60">
         <v>0.73517089832787508</v>
@@ -5630,7 +5630,7 @@
     </row>
     <row r="61" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B61">
         <v>0.88404552668858538</v>
@@ -5708,7 +5708,7 @@
     </row>
     <row r="62" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B62">
         <v>0.8257790059284793</v>
@@ -5786,7 +5786,7 @@
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B63">
         <v>1.159748470842791</v>
@@ -5864,7 +5864,7 @@
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B64">
         <v>0.5794416800406591</v>
@@ -5942,7 +5942,7 @@
     </row>
     <row r="65" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B65">
         <v>0.84742289605813803</v>
@@ -6020,7 +6020,7 @@
     </row>
     <row r="66" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B66">
         <v>0.64347592150852451</v>
@@ -6098,7 +6098,7 @@
     </row>
     <row r="67" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B67">
         <v>0.57678609282112236</v>
@@ -6176,7 +6176,7 @@
     </row>
     <row r="68" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B68">
         <v>0.67181268619517298</v>
@@ -6254,7 +6254,7 @@
     </row>
     <row r="69" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B69">
         <v>1.0260931909001121</v>
@@ -6332,7 +6332,7 @@
     </row>
     <row r="70" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B70">
         <v>0.44524570466648722</v>
@@ -6410,7 +6410,7 @@
     </row>
     <row r="71" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B71">
         <v>0.38899371272107952</v>
@@ -6488,7 +6488,7 @@
     </row>
     <row r="72" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B72">
         <v>0.89540061279387873</v>
@@ -6566,7 +6566,7 @@
     </row>
     <row r="73" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B73">
         <v>0.3190761762360167</v>
@@ -6644,7 +6644,7 @@
     </row>
     <row r="74" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B74">
         <v>0.98918620258196766</v>
@@ -6722,7 +6722,7 @@
     </row>
     <row r="75" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B75">
         <v>0.88810140774148982</v>
@@ -6800,7 +6800,7 @@
     </row>
     <row r="76" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B76">
         <v>0.57711740736795858</v>
@@ -6878,7 +6878,7 @@
     </row>
     <row r="77" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B77">
         <v>0.97073642673972049</v>
@@ -6956,7 +6956,7 @@
     </row>
     <row r="78" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B78">
         <v>0.71341355355073421</v>
@@ -7016,7 +7016,7 @@
     </row>
     <row r="79" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B79">
         <v>0.71481030231411657</v>
@@ -7094,7 +7094,7 @@
     </row>
     <row r="80" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B80">
         <v>0.70293109584927627</v>
@@ -7172,7 +7172,7 @@
     </row>
     <row r="81" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B81">
         <v>0.66695416852303913</v>
@@ -7250,7 +7250,7 @@
     </row>
     <row r="82" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B82">
         <v>0.92890899827092466</v>
@@ -7328,7 +7328,7 @@
     </row>
     <row r="83" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B83">
         <v>0.66164971786092408</v>
@@ -7406,7 +7406,7 @@
     </row>
     <row r="84" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B84">
         <v>1.0376691456299789</v>
@@ -7484,7 +7484,7 @@
     </row>
     <row r="85" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B85">
         <v>0.83440385593770527</v>
@@ -7562,7 +7562,7 @@
     </row>
     <row r="86" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B86">
         <v>0.71182370092865688</v>
@@ -7640,7 +7640,7 @@
     </row>
     <row r="87" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B87">
         <v>0.56057290844723529</v>
@@ -7718,7 +7718,7 @@
     </row>
     <row r="88" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B88">
         <v>0.86399241381241088</v>
@@ -7796,7 +7796,7 @@
     </row>
     <row r="89" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B89">
         <v>0.94721117392206522</v>
@@ -7874,7 +7874,7 @@
     </row>
     <row r="90" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B90">
         <v>1.081733739171107</v>
@@ -7952,7 +7952,7 @@
     </row>
     <row r="91" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B91">
         <v>0.8388277494866474</v>
@@ -8030,7 +8030,7 @@
     </row>
     <row r="92" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B92">
         <v>0.98924096258683591</v>
@@ -8105,7 +8105,7 @@
     </row>
     <row r="93" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B93">
         <v>0.53279835591625591</v>
@@ -8183,7 +8183,7 @@
     </row>
     <row r="94" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B94">
         <v>0.56313205148312573</v>
@@ -8261,7 +8261,7 @@
     </row>
     <row r="95" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B95">
         <v>1.074555473472828</v>
@@ -8339,7 +8339,7 @@
     </row>
     <row r="96" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B96">
         <v>0.66650572225468585</v>
@@ -8417,7 +8417,7 @@
     </row>
     <row r="97" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B97">
         <v>1.147186410540457</v>
@@ -8495,7 +8495,7 @@
     </row>
     <row r="98" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B98">
         <v>0.77290815753918252</v>
@@ -8573,7 +8573,7 @@
     </row>
     <row r="99" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B99">
         <v>0.93178313256814138</v>
@@ -8651,7 +8651,7 @@
     </row>
     <row r="100" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B100">
         <v>1.030530181939125</v>
@@ -8729,7 +8729,7 @@
     </row>
     <row r="101" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B101">
         <v>0.76939906099868915</v>
@@ -8807,7 +8807,7 @@
     </row>
     <row r="102" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B102">
         <v>0.95499683626513376</v>
@@ -8885,7 +8885,7 @@
     </row>
     <row r="103" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B103">
         <v>0.97666188813563548</v>
@@ -8963,7 +8963,7 @@
     </row>
     <row r="104" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B104">
         <v>0.74033870274340763</v>
@@ -9041,7 +9041,7 @@
     </row>
     <row r="105" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B105">
         <v>1.2141458779617229</v>
@@ -9119,7 +9119,7 @@
     </row>
     <row r="106" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B106">
         <v>1.1076180623581089</v>
@@ -9197,7 +9197,7 @@
     </row>
     <row r="107" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B107">
         <v>0.80732727779110824</v>
@@ -9275,7 +9275,7 @@
     </row>
     <row r="108" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B108">
         <v>1.095023675923011</v>
@@ -9353,7 +9353,7 @@
     </row>
     <row r="109" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B109">
         <v>1.0436836035193351</v>
@@ -9431,7 +9431,7 @@
     </row>
     <row r="110" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B110">
         <v>0.9249946236035862</v>
@@ -9509,7 +9509,7 @@
     </row>
     <row r="111" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B111">
         <v>0.72607981527595333</v>
@@ -9587,7 +9587,7 @@
     </row>
     <row r="112" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B112">
         <v>0.33286110713971018</v>
@@ -9665,7 +9665,7 @@
     </row>
     <row r="113" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B113">
         <v>0.59879055133173775</v>
@@ -9743,7 +9743,7 @@
     </row>
     <row r="114" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B114">
         <v>0.51457753381825666</v>
@@ -9818,7 +9818,7 @@
     </row>
     <row r="115" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B115">
         <v>0.98903069477865735</v>
@@ -9896,7 +9896,7 @@
     </row>
     <row r="116" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B116">
         <v>0.83663101973534415</v>
@@ -9974,7 +9974,7 @@
     </row>
     <row r="117" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B117">
         <v>0.71422592821984132</v>
@@ -10052,7 +10052,7 @@
     </row>
     <row r="118" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B118">
         <v>0.90648089208204907</v>
@@ -10130,7 +10130,7 @@
     </row>
     <row r="119" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B119">
         <v>0.81272828662341823</v>
@@ -10208,7 +10208,7 @@
     </row>
     <row r="120" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B120">
         <v>0.44722986554851513</v>
@@ -10286,7 +10286,7 @@
     </row>
     <row r="121" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B121">
         <v>0.54388240454450099</v>
@@ -10364,7 +10364,7 @@
     </row>
     <row r="122" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B122">
         <v>0.67016054627289945</v>
@@ -10442,7 +10442,7 @@
     </row>
     <row r="123" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B123">
         <v>0.76189493031299316</v>
@@ -10520,7 +10520,7 @@
     </row>
     <row r="124" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B124">
         <v>1.028795008683723</v>
@@ -10598,7 +10598,7 @@
     </row>
     <row r="125" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B125">
         <v>1.25808986916217</v>
@@ -10676,7 +10676,7 @@
     </row>
     <row r="126" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B126">
         <v>0.78060077263843985</v>
@@ -10754,7 +10754,7 @@
     </row>
     <row r="127" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B127">
         <v>0.61270336494941691</v>
@@ -10832,7 +10832,7 @@
     </row>
     <row r="128" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B128">
         <v>0.8569031797012614</v>
@@ -10910,7 +10910,7 @@
     </row>
     <row r="129" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B129">
         <v>0.76837457188754066</v>
@@ -10985,7 +10985,7 @@
     </row>
     <row r="130" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B130">
         <v>0.8648966284889702</v>
@@ -11060,7 +11060,7 @@
     </row>
     <row r="131" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B131">
         <v>0.85292210706055782</v>
@@ -11138,7 +11138,7 @@
     </row>
     <row r="132" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B132">
         <v>0.84976419949326787</v>
@@ -11213,7 +11213,7 @@
     </row>
     <row r="133" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B133">
         <v>1.0334484763771561</v>
@@ -11288,7 +11288,7 @@
     </row>
     <row r="134" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B134">
         <v>0.93959564287166764</v>
@@ -11363,7 +11363,7 @@
     </row>
     <row r="135" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B135">
         <v>0.51973174542624856</v>
@@ -11441,7 +11441,7 @@
     </row>
     <row r="136" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B136">
         <v>0.6517839543955195</v>
@@ -11516,7 +11516,7 @@
     </row>
     <row r="137" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B137">
         <v>0.48649167430360329</v>
@@ -11594,7 +11594,7 @@
     </row>
     <row r="138" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B138">
         <v>0.48317949302228291</v>
@@ -11672,7 +11672,7 @@
     </row>
     <row r="139" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B139">
         <v>0.62031038988323939</v>
@@ -11750,7 +11750,7 @@
     </row>
     <row r="140" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B140">
         <v>0.55617356483404023</v>
@@ -11828,7 +11828,7 @@
     </row>
     <row r="141" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B141">
         <v>0.6813450407301489</v>
@@ -11906,7 +11906,7 @@
     </row>
     <row r="142" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B142">
         <v>0.41938342246895027</v>
@@ -11966,7 +11966,7 @@
     </row>
     <row r="143" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B143">
         <v>0.83535725304426744</v>
@@ -12041,7 +12041,7 @@
     </row>
     <row r="144" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B144">
         <v>0.66998829276589156</v>
@@ -12116,7 +12116,7 @@
     </row>
     <row r="145" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B145">
         <v>0.65536947942371004</v>
@@ -12194,7 +12194,7 @@
     </row>
     <row r="146" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B146">
         <v>0.53989066386687967</v>
@@ -12272,7 +12272,7 @@
     </row>
     <row r="147" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B147">
         <v>0.59265442111176048</v>
@@ -12347,7 +12347,7 @@
     </row>
     <row r="148" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B148">
         <v>0.51606180450747374</v>
@@ -12422,7 +12422,7 @@
     </row>
     <row r="149" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B149">
         <v>0.576450045976727</v>
@@ -12500,7 +12500,7 @@
     </row>
     <row r="150" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B150">
         <v>0.74583079975844124</v>
@@ -12578,7 +12578,7 @@
     </row>
     <row r="151" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B151">
         <v>0.74382229176850467</v>
@@ -12656,7 +12656,7 @@
     </row>
     <row r="152" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B152">
         <v>0.52873724477449735</v>
@@ -12734,7 +12734,7 @@
     </row>
     <row r="153" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B153">
         <v>0.75719209664775033</v>
@@ -12812,7 +12812,7 @@
     </row>
     <row r="154" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B154">
         <v>0.45212381984381461</v>
@@ -12890,7 +12890,7 @@
     </row>
     <row r="155" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G155">
         <v>12.423314200840929</v>
@@ -12953,7 +12953,7 @@
     </row>
     <row r="156" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B156">
         <v>0.74703881086094448</v>
@@ -13028,7 +13028,7 @@
     </row>
     <row r="157" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B157">
         <v>0.79343278584490906</v>
@@ -13088,7 +13088,7 @@
     </row>
     <row r="158" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B158">
         <v>0.71931541902066587</v>
@@ -13166,7 +13166,7 @@
     </row>
     <row r="159" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B159">
         <v>0.8019650196542859</v>
@@ -13244,7 +13244,7 @@
     </row>
     <row r="160" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B160">
         <v>0.81483604731780046</v>
@@ -13322,7 +13322,7 @@
     </row>
     <row r="161" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B161">
         <v>0.65994702023433482</v>
@@ -13397,7 +13397,7 @@
     </row>
     <row r="162" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B162">
         <v>0.6563452010995684</v>
@@ -13475,7 +13475,7 @@
     </row>
     <row r="163" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B163">
         <v>0.94252060567468432</v>
@@ -13553,7 +13553,7 @@
     </row>
     <row r="164" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B164">
         <v>0.70589730680432128</v>
@@ -13631,7 +13631,7 @@
     </row>
     <row r="165" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B165">
         <v>0.8982631833584851</v>
@@ -13709,7 +13709,7 @@
     </row>
     <row r="166" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B166">
         <v>0.68031418974397462</v>
@@ -13787,7 +13787,7 @@
     </row>
     <row r="167" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H167">
         <v>169.13917927925621</v>
@@ -13847,7 +13847,7 @@
     </row>
     <row r="168" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B168">
         <v>0.68700114206256468</v>
@@ -13883,7 +13883,7 @@
     </row>
     <row r="169" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B169">
         <v>0.73189428563880166</v>

--- a/ROSA_vitaSPEC/Data/Analyses_chimiques_4var_en_plus_HR.xlsx
+++ b/ROSA_vitaSPEC/Data/Analyses_chimiques_4var_en_plus_HR.xlsx
@@ -956,6 +956,7 @@
     <col min="14" max="14" width="20" customWidth="1"/>
     <col min="15" max="15" width="23.42578125" customWidth="1"/>
     <col min="16" max="16" width="21.7109375" customWidth="1"/>
+    <col min="17" max="17" width="17" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.25">
